--- a/quizzes/sculpture-19e-niveau1.xlsx
+++ b/quizzes/sculpture-19e-niveau1.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B798AAA-C23E-4C44-8D17-455A70099402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266C24CE-3E78-4859-ABD6-EED136E5FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="1110" windowWidth="15270" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top 30 sculpteurs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
   <si>
     <t>image</t>
   </si>
@@ -49,18 +62,9 @@
     <t>Le Penseur</t>
   </si>
   <si>
-    <t>Antonio Canova</t>
-  </si>
-  <si>
-    <t>1793</t>
-  </si>
-  <si>
     <t>Musée du Louvre, Paris</t>
   </si>
   <si>
-    <t>Psyché ranimée par le baiser de l'Amour</t>
-  </si>
-  <si>
     <t>Bertel Thorvaldsen</t>
   </si>
   <si>
@@ -148,18 +152,6 @@
     <t>Monument à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
   </si>
   <si>
-    <t>Daniel Chester French</t>
-  </si>
-  <si>
-    <t>1911-1920</t>
-  </si>
-  <si>
-    <t>Lincoln Memorial, Washington</t>
-  </si>
-  <si>
-    <t>Abraham Lincoln (Lincoln Memorial)</t>
-  </si>
-  <si>
     <t>David d'Angers</t>
   </si>
   <si>
@@ -193,18 +185,6 @@
     <t>Éros (fontaine commémorative Shaftesbury)</t>
   </si>
   <si>
-    <t>Gustav Vigeland</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>Parc Vigeland, Oslo</t>
-  </si>
-  <si>
-    <t>Le Petit Garçon en colère (Sinnataggen)</t>
-  </si>
-  <si>
     <t>Josef Václav Myslbek</t>
   </si>
   <si>
@@ -331,15 +311,6 @@
     <t>Gloria Victis</t>
   </si>
   <si>
-    <t>Johann Gottfried Schadow</t>
-  </si>
-  <si>
-    <t>Porte de Brandebourg, Berlin</t>
-  </si>
-  <si>
-    <t>Quadrige de la Porte de Brandebourg</t>
-  </si>
-  <si>
     <t>Jean-Léon Gérôme</t>
   </si>
   <si>
@@ -373,9 +344,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg/960px-Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG/1280px-0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -400,9 +368,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif/lossy-page1-1280px-Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -412,9 +377,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg/1280px-Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -448,9 +410,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d1/Restored_quadriga_atop_Brandenburg_Gate.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -470,6 +429,39 @@
   </si>
   <si>
     <t>Auguste Bartholdi</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Albert-Ernest Carrier-Belleuse</t>
+  </si>
+  <si>
+    <t>1863</t>
+  </si>
+  <si>
+    <t>La Bacchante</t>
+  </si>
+  <si>
+    <t>Edgard Degas</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste Clésinger</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>1878-1881</t>
+  </si>
+  <si>
+    <t>La Petite Danseuse de quatorze ans (1er modèle en cire)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Femme piquée par un serpent</t>
   </si>
 </sst>
 </file>
@@ -517,17 +509,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -535,21 +528,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -855,17 +867,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="5" max="5" width="73.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.95" customHeight="1">
+    <row r="1" spans="1:49" ht="24.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,533 +893,2432 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="6" customFormat="1">
-      <c r="A2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="6" customFormat="1">
-      <c r="A3" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+    </row>
+    <row r="2" spans="1:49" s="2" customFormat="1">
+      <c r="A2" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
+      <c r="AW2" s="3"/>
+    </row>
+    <row r="3" spans="1:49" s="2" customFormat="1">
+      <c r="A3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="6" customFormat="1">
-      <c r="A5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+    </row>
+    <row r="4" spans="1:49">
+      <c r="A4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="6" customFormat="1">
-      <c r="A6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+    </row>
+    <row r="5" spans="1:49" s="2" customFormat="1">
+      <c r="A5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>149</v>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+      <c r="AO5" s="3"/>
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3"/>
+      <c r="AT5" s="3"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+    </row>
+    <row r="6" spans="1:49" s="2" customFormat="1">
+      <c r="A6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+    </row>
+    <row r="7" spans="1:49" s="2" customFormat="1">
+      <c r="A7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C7" s="8">
         <v>1886</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="6" customFormat="1">
-      <c r="A8" s="4" t="s">
+      <c r="D7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+    </row>
+    <row r="8" spans="1:49">
+      <c r="A8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+    </row>
+    <row r="9" spans="1:49" s="2" customFormat="1">
+      <c r="A9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
+      <c r="AU9" s="3"/>
+      <c r="AV9" s="3"/>
+      <c r="AW9" s="3"/>
+    </row>
+    <row r="10" spans="1:49" s="2" customFormat="1">
+      <c r="A10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="3"/>
+      <c r="AT10" s="3"/>
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="3"/>
+      <c r="AW10" s="3"/>
+    </row>
+    <row r="11" spans="1:49">
+      <c r="A11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
+    </row>
+    <row r="12" spans="1:49">
+      <c r="A12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+      <c r="AQ12" s="3"/>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3"/>
+      <c r="AT12" s="3"/>
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="3"/>
+      <c r="AW12" s="3"/>
+    </row>
+    <row r="13" spans="1:49">
+      <c r="A13" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3"/>
+      <c r="AT13" s="3"/>
+      <c r="AU13" s="3"/>
+      <c r="AV13" s="3"/>
+      <c r="AW13" s="3"/>
+    </row>
+    <row r="14" spans="1:49">
+      <c r="A14" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="3"/>
+      <c r="AU14" s="3"/>
+      <c r="AV14" s="3"/>
+      <c r="AW14" s="3"/>
+    </row>
+    <row r="15" spans="1:49">
+      <c r="A15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3"/>
+      <c r="AU15" s="3"/>
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3"/>
+    </row>
+    <row r="16" spans="1:49">
+      <c r="A16" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3"/>
+      <c r="AT16" s="3"/>
+      <c r="AU16" s="3"/>
+      <c r="AV16" s="3"/>
+      <c r="AW16" s="3"/>
+    </row>
+    <row r="17" spans="1:49">
+      <c r="A17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3"/>
+      <c r="AT17" s="3"/>
+      <c r="AU17" s="3"/>
+      <c r="AV17" s="3"/>
+      <c r="AW17" s="3"/>
+    </row>
+    <row r="18" spans="1:49">
+      <c r="A18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3"/>
+      <c r="AT18" s="3"/>
+      <c r="AU18" s="3"/>
+      <c r="AV18" s="3"/>
+      <c r="AW18" s="3"/>
+    </row>
+    <row r="19" spans="1:49">
+      <c r="A19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+    </row>
+    <row r="20" spans="1:49">
+      <c r="A20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="3"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="3"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3"/>
+      <c r="AT20" s="3"/>
+      <c r="AU20" s="3"/>
+      <c r="AV20" s="3"/>
+      <c r="AW20" s="3"/>
+    </row>
+    <row r="21" spans="1:49" s="2" customFormat="1">
+      <c r="A21" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1847</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="3"/>
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="3"/>
+      <c r="AQ21" s="3"/>
+      <c r="AR21" s="3"/>
+      <c r="AS21" s="3"/>
+      <c r="AT21" s="3"/>
+      <c r="AU21" s="3"/>
+      <c r="AV21" s="3"/>
+      <c r="AW21" s="3"/>
+    </row>
+    <row r="22" spans="1:49">
+      <c r="A22" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3"/>
+      <c r="AT22" s="3"/>
+      <c r="AU22" s="3"/>
+      <c r="AV22" s="3"/>
+      <c r="AW22" s="3"/>
+    </row>
+    <row r="23" spans="1:49">
+      <c r="A23" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="3"/>
+      <c r="AT23" s="3"/>
+      <c r="AU23" s="3"/>
+      <c r="AV23" s="3"/>
+      <c r="AW23" s="3"/>
+    </row>
+    <row r="24" spans="1:49">
+      <c r="A24" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="6" customFormat="1">
-      <c r="A9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="6" customFormat="1">
-      <c r="A10" s="3" t="s">
+      <c r="B24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="3"/>
+      <c r="AQ24" s="3"/>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="3"/>
+      <c r="AT24" s="3"/>
+      <c r="AU24" s="3"/>
+      <c r="AV24" s="3"/>
+      <c r="AW24" s="3"/>
+    </row>
+    <row r="25" spans="1:49">
+      <c r="A25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+    </row>
+    <row r="26" spans="1:49">
+      <c r="A26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="3"/>
+      <c r="AU26" s="3"/>
+      <c r="AV26" s="3"/>
+      <c r="AW26" s="3"/>
+    </row>
+    <row r="27" spans="1:49">
+      <c r="A27" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="3"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="3"/>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="3"/>
+      <c r="AT27" s="3"/>
+      <c r="AU27" s="3"/>
+      <c r="AV27" s="3"/>
+      <c r="AW27" s="3"/>
+    </row>
+    <row r="28" spans="1:49">
+      <c r="A28" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="3"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="3"/>
+      <c r="AT28" s="3"/>
+      <c r="AU28" s="3"/>
+      <c r="AV28" s="3"/>
+      <c r="AW28" s="3"/>
+    </row>
+    <row r="29" spans="1:49">
+      <c r="A29" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="B29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="3"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="3"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="3"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="3"/>
+      <c r="AT29" s="3"/>
+      <c r="AU29" s="3"/>
+      <c r="AV29" s="3"/>
+      <c r="AW29" s="3"/>
+    </row>
+    <row r="30" spans="1:49">
+      <c r="A30" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="6" customFormat="1">
-      <c r="A13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="6" customFormat="1">
-      <c r="A14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="B30" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="3"/>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3"/>
+      <c r="AM30" s="3"/>
+      <c r="AN30" s="3"/>
+      <c r="AO30" s="3"/>
+      <c r="AP30" s="3"/>
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3"/>
+      <c r="AT30" s="3"/>
+      <c r="AU30" s="3"/>
+      <c r="AV30" s="3"/>
+      <c r="AW30" s="3"/>
+    </row>
+    <row r="31" spans="1:49">
+      <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="6" customFormat="1">
-      <c r="A27" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B31" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C31" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="D31" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="E31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3"/>
+      <c r="AJ31" s="3"/>
+      <c r="AK31" s="3"/>
+      <c r="AL31" s="3"/>
+      <c r="AM31" s="3"/>
+      <c r="AN31" s="3"/>
+      <c r="AO31" s="3"/>
+      <c r="AP31" s="3"/>
+      <c r="AQ31" s="3"/>
+      <c r="AR31" s="3"/>
+      <c r="AS31" s="3"/>
+      <c r="AT31" s="3"/>
+      <c r="AU31" s="3"/>
+      <c r="AV31" s="3"/>
+      <c r="AW31" s="3"/>
+    </row>
+    <row r="32" spans="1:49">
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3"/>
+      <c r="AK32" s="3"/>
+      <c r="AL32" s="3"/>
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="3"/>
+      <c r="AO32" s="3"/>
+      <c r="AP32" s="3"/>
+      <c r="AQ32" s="3"/>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="3"/>
+      <c r="AT32" s="3"/>
+      <c r="AU32" s="3"/>
+      <c r="AV32" s="3"/>
+      <c r="AW32" s="3"/>
+    </row>
+    <row r="33" spans="6:49">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="3"/>
+      <c r="AJ33" s="3"/>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="3"/>
+      <c r="AM33" s="3"/>
+      <c r="AN33" s="3"/>
+      <c r="AO33" s="3"/>
+      <c r="AP33" s="3"/>
+      <c r="AQ33" s="3"/>
+      <c r="AR33" s="3"/>
+      <c r="AS33" s="3"/>
+      <c r="AT33" s="3"/>
+      <c r="AU33" s="3"/>
+      <c r="AV33" s="3"/>
+      <c r="AW33" s="3"/>
+    </row>
+    <row r="34" spans="6:49">
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="3"/>
+      <c r="AK34" s="3"/>
+      <c r="AL34" s="3"/>
+      <c r="AM34" s="3"/>
+      <c r="AN34" s="3"/>
+      <c r="AO34" s="3"/>
+      <c r="AP34" s="3"/>
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="3"/>
+      <c r="AT34" s="3"/>
+      <c r="AU34" s="3"/>
+      <c r="AV34" s="3"/>
+      <c r="AW34" s="3"/>
+    </row>
+    <row r="35" spans="6:49">
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="3"/>
+      <c r="AJ35" s="3"/>
+      <c r="AK35" s="3"/>
+      <c r="AL35" s="3"/>
+      <c r="AM35" s="3"/>
+      <c r="AN35" s="3"/>
+      <c r="AO35" s="3"/>
+      <c r="AP35" s="3"/>
+      <c r="AQ35" s="3"/>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="3"/>
+      <c r="AT35" s="3"/>
+      <c r="AU35" s="3"/>
+      <c r="AV35" s="3"/>
+      <c r="AW35" s="3"/>
+    </row>
+    <row r="36" spans="6:49">
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="3"/>
+      <c r="AI36" s="3"/>
+      <c r="AJ36" s="3"/>
+      <c r="AK36" s="3"/>
+      <c r="AL36" s="3"/>
+      <c r="AM36" s="3"/>
+      <c r="AN36" s="3"/>
+      <c r="AO36" s="3"/>
+      <c r="AP36" s="3"/>
+      <c r="AQ36" s="3"/>
+      <c r="AR36" s="3"/>
+      <c r="AS36" s="3"/>
+      <c r="AT36" s="3"/>
+      <c r="AU36" s="3"/>
+      <c r="AV36" s="3"/>
+      <c r="AW36" s="3"/>
+    </row>
+    <row r="37" spans="6:49">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+      <c r="AI37" s="3"/>
+      <c r="AJ37" s="3"/>
+      <c r="AK37" s="3"/>
+      <c r="AL37" s="3"/>
+      <c r="AM37" s="3"/>
+      <c r="AN37" s="3"/>
+      <c r="AO37" s="3"/>
+      <c r="AP37" s="3"/>
+      <c r="AQ37" s="3"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="3"/>
+      <c r="AT37" s="3"/>
+      <c r="AU37" s="3"/>
+      <c r="AV37" s="3"/>
+      <c r="AW37" s="3"/>
+    </row>
+    <row r="38" spans="6:49">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="3"/>
+      <c r="AK38" s="3"/>
+      <c r="AL38" s="3"/>
+      <c r="AM38" s="3"/>
+      <c r="AN38" s="3"/>
+      <c r="AO38" s="3"/>
+      <c r="AP38" s="3"/>
+      <c r="AQ38" s="3"/>
+      <c r="AR38" s="3"/>
+      <c r="AS38" s="3"/>
+      <c r="AT38" s="3"/>
+      <c r="AU38" s="3"/>
+      <c r="AV38" s="3"/>
+      <c r="AW38" s="3"/>
+    </row>
+    <row r="39" spans="6:49">
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="3"/>
+      <c r="AT39" s="3"/>
+      <c r="AU39" s="3"/>
+      <c r="AV39" s="3"/>
+      <c r="AW39" s="3"/>
+    </row>
+    <row r="40" spans="6:49">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
+      <c r="AS40" s="3"/>
+      <c r="AT40" s="3"/>
+      <c r="AU40" s="3"/>
+      <c r="AV40" s="3"/>
+      <c r="AW40" s="3"/>
+    </row>
+    <row r="41" spans="6:49">
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="3"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="3"/>
+      <c r="AK41" s="3"/>
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="3"/>
+      <c r="AN41" s="3"/>
+      <c r="AO41" s="3"/>
+      <c r="AP41" s="3"/>
+      <c r="AQ41" s="3"/>
+      <c r="AR41" s="3"/>
+      <c r="AS41" s="3"/>
+      <c r="AT41" s="3"/>
+      <c r="AU41" s="3"/>
+      <c r="AV41" s="3"/>
+      <c r="AW41" s="3"/>
+    </row>
+    <row r="42" spans="6:49">
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
+      <c r="AC42" s="3"/>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="3"/>
+      <c r="AH42" s="3"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="3"/>
+      <c r="AK42" s="3"/>
+      <c r="AL42" s="3"/>
+      <c r="AM42" s="3"/>
+      <c r="AN42" s="3"/>
+      <c r="AO42" s="3"/>
+      <c r="AP42" s="3"/>
+      <c r="AQ42" s="3"/>
+      <c r="AR42" s="3"/>
+      <c r="AS42" s="3"/>
+      <c r="AT42" s="3"/>
+      <c r="AU42" s="3"/>
+      <c r="AV42" s="3"/>
+      <c r="AW42" s="3"/>
+    </row>
+    <row r="43" spans="6:49">
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="3"/>
+      <c r="AC43" s="3"/>
+      <c r="AD43" s="3"/>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="3"/>
+      <c r="AH43" s="3"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="3"/>
+      <c r="AK43" s="3"/>
+      <c r="AL43" s="3"/>
+      <c r="AM43" s="3"/>
+      <c r="AN43" s="3"/>
+      <c r="AO43" s="3"/>
+      <c r="AP43" s="3"/>
+      <c r="AQ43" s="3"/>
+      <c r="AR43" s="3"/>
+      <c r="AS43" s="3"/>
+      <c r="AT43" s="3"/>
+      <c r="AU43" s="3"/>
+      <c r="AV43" s="3"/>
+      <c r="AW43" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E32">
@@ -1415,36 +3326,35 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A8" r:id="rId1" xr:uid="{93AE980A-6B12-46F0-A8CF-A0D01340DED5}"/>
-    <hyperlink ref="A6" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG/1280px-0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5DA36176-0E18-48E2-BCA7-5A9CE7168BFC}"/>
-    <hyperlink ref="A10" r:id="rId3" xr:uid="{0279C923-D2AA-4264-A899-0BCAFCC5DD8C}"/>
-    <hyperlink ref="A11" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{53D6ACD5-B359-40B4-A22C-BB1BD3A81A04}"/>
-    <hyperlink ref="A21" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C9618ED-B2D7-4284-AD04-539CA4892DAB}"/>
-    <hyperlink ref="A4" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{37B3A290-0452-476D-8FC2-55660C65251D}"/>
-    <hyperlink ref="A16" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B0DB905-2A62-400D-AF1A-5AD350CF3CD4}"/>
-    <hyperlink ref="A15" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7DDC986B-350E-4853-AFD0-B0E19187033D}"/>
-    <hyperlink ref="A20" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AF2F99B6-B0A4-4A9F-A44A-080AD9DF2FFA}"/>
-    <hyperlink ref="A9" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6A325E4D-8BB3-40C0-87DB-8F413F02DF10}"/>
-    <hyperlink ref="A12" r:id="rId11" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif/lossy-page1-1280px-Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5A9F48FE-9265-4FB8-B364-2121A5C4D800}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{4B3D9FD6-66B2-486E-91BD-1D9D62B49EB7}"/>
-    <hyperlink ref="A27" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E5AA8D6E-B554-44B0-9598-E37ED9C0B7BD}"/>
-    <hyperlink ref="A2" r:id="rId14" xr:uid="{5A5F0717-4C25-4354-B29B-0BB266B96FCF}"/>
-    <hyperlink ref="A18" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg/1280px-Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BCA4B0F6-030C-4CCD-A9BE-8ADCDB97DADF}"/>
-    <hyperlink ref="A26" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{23816190-EF7C-44C9-ADDC-EAA4146655D3}"/>
-    <hyperlink ref="A19" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7CC8B167-A92F-4D6C-89C1-9BE59C7CF5A4}"/>
-    <hyperlink ref="A25" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{92062880-0FD1-4CE9-A7CF-BDDB3CA8A045}"/>
-    <hyperlink ref="A29" r:id="rId19" xr:uid="{843C53DE-19DB-442D-B85C-710A65F939C3}"/>
-    <hyperlink ref="A30" r:id="rId20" xr:uid="{4C55E7F3-65D4-41C2-88DF-18F00C27A935}"/>
-    <hyperlink ref="A31" r:id="rId21" xr:uid="{261C79ED-8811-43FF-BD7A-B3653CD9C364}"/>
-    <hyperlink ref="A32" r:id="rId22" xr:uid="{6A6F7BA2-54C9-4A0E-B208-8664C78E75F7}"/>
-    <hyperlink ref="A14" r:id="rId23" xr:uid="{62C8B9DF-387B-4E1A-A861-168C2C139E02}"/>
-    <hyperlink ref="A17" r:id="rId24" xr:uid="{4DD3F97F-7316-49A3-9B11-B959E5E59F76}"/>
-    <hyperlink ref="A28" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8AE5868-74B7-4C36-A835-D4B1EDCBB97C}"/>
-    <hyperlink ref="A5" r:id="rId26" xr:uid="{A4A753D4-9A9F-4B52-ACE5-7932A6E3BF1E}"/>
-    <hyperlink ref="A24" r:id="rId27" xr:uid="{3D1119C9-40FA-4A90-B0DF-F18DFD07E039}"/>
-    <hyperlink ref="A22" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090BCA57-D77A-4463-8E66-36EC42C0B0F0}"/>
-    <hyperlink ref="A23" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE250664-62F3-4370-B90E-2020D4EB3180}"/>
-    <hyperlink ref="A3" r:id="rId30" xr:uid="{DD90777D-C6DF-4044-9591-4C77E277C2F7}"/>
-    <hyperlink ref="A7" r:id="rId31" xr:uid="{976DAD26-1E55-4BD4-AF6C-2386561AB7EE}"/>
+    <hyperlink ref="A10" r:id="rId2" xr:uid="{0279C923-D2AA-4264-A899-0BCAFCC5DD8C}"/>
+    <hyperlink ref="A11" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{53D6ACD5-B359-40B4-A22C-BB1BD3A81A04}"/>
+    <hyperlink ref="A20" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C9618ED-B2D7-4284-AD04-539CA4892DAB}"/>
+    <hyperlink ref="A5" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{37B3A290-0452-476D-8FC2-55660C65251D}"/>
+    <hyperlink ref="A16" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B0DB905-2A62-400D-AF1A-5AD350CF3CD4}"/>
+    <hyperlink ref="A15" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7DDC986B-350E-4853-AFD0-B0E19187033D}"/>
+    <hyperlink ref="A19" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AF2F99B6-B0A4-4A9F-A44A-080AD9DF2FFA}"/>
+    <hyperlink ref="A9" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6A325E4D-8BB3-40C0-87DB-8F413F02DF10}"/>
+    <hyperlink ref="A12" r:id="rId10" xr:uid="{4B3D9FD6-66B2-486E-91BD-1D9D62B49EB7}"/>
+    <hyperlink ref="A26" r:id="rId11" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E5AA8D6E-B554-44B0-9598-E37ED9C0B7BD}"/>
+    <hyperlink ref="A3" r:id="rId12" xr:uid="{5A5F0717-4C25-4354-B29B-0BB266B96FCF}"/>
+    <hyperlink ref="A25" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{23816190-EF7C-44C9-ADDC-EAA4146655D3}"/>
+    <hyperlink ref="A18" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7CC8B167-A92F-4D6C-89C1-9BE59C7CF5A4}"/>
+    <hyperlink ref="A24" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{92062880-0FD1-4CE9-A7CF-BDDB3CA8A045}"/>
+    <hyperlink ref="A28" r:id="rId16" xr:uid="{843C53DE-19DB-442D-B85C-710A65F939C3}"/>
+    <hyperlink ref="A29" r:id="rId17" xr:uid="{4C55E7F3-65D4-41C2-88DF-18F00C27A935}"/>
+    <hyperlink ref="A30" r:id="rId18" xr:uid="{261C79ED-8811-43FF-BD7A-B3653CD9C364}"/>
+    <hyperlink ref="A31" r:id="rId19" xr:uid="{6A6F7BA2-54C9-4A0E-B208-8664C78E75F7}"/>
+    <hyperlink ref="A14" r:id="rId20" xr:uid="{62C8B9DF-387B-4E1A-A861-168C2C139E02}"/>
+    <hyperlink ref="A17" r:id="rId21" xr:uid="{4DD3F97F-7316-49A3-9B11-B959E5E59F76}"/>
+    <hyperlink ref="A27" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8AE5868-74B7-4C36-A835-D4B1EDCBB97C}"/>
+    <hyperlink ref="A6" r:id="rId23" xr:uid="{A4A753D4-9A9F-4B52-ACE5-7932A6E3BF1E}"/>
+    <hyperlink ref="A22" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090BCA57-D77A-4463-8E66-36EC42C0B0F0}"/>
+    <hyperlink ref="A23" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE250664-62F3-4370-B90E-2020D4EB3180}"/>
+    <hyperlink ref="A4" r:id="rId26" xr:uid="{DD90777D-C6DF-4044-9591-4C77E277C2F7}"/>
+    <hyperlink ref="A7" r:id="rId27" xr:uid="{976DAD26-1E55-4BD4-AF6C-2386561AB7EE}"/>
+    <hyperlink ref="A2" r:id="rId28" xr:uid="{17830633-D13B-44E2-A398-05B0D9312C22}"/>
+    <hyperlink ref="A13" r:id="rId29" xr:uid="{C75D6FEC-65CF-4FF8-B661-4610575911B6}"/>
+    <hyperlink ref="A21" r:id="rId30" xr:uid="{A47C825E-3623-4ADD-83EC-C19C17B5E457}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-19e-niveau1.xlsx
+++ b/quizzes/sculpture-19e-niveau1.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266C24CE-3E78-4859-ABD6-EED136E5FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B83046-84DD-4EDA-9EB3-3C5A97D5DE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top 30 sculpteurs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="213">
   <si>
     <t>image</t>
   </si>
@@ -50,6 +37,162 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
+    <t>dates artiste</t>
+  </si>
+  <si>
+    <t>Matériaux et technique</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Albert-Ernest Carrier-Belleuse</t>
+  </si>
+  <si>
+    <t>1863</t>
+  </si>
+  <si>
+    <t>Musée d'Orsay, Paris</t>
+  </si>
+  <si>
+    <t>La Bacchante</t>
+  </si>
+  <si>
+    <t>1824-1887</t>
+  </si>
+  <si>
+    <t>Marbre</t>
+  </si>
+  <si>
+    <t>environ 90 cm de haut</t>
+  </si>
+  <si>
+    <t>française</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Alfred Gilbert</t>
+  </si>
+  <si>
+    <t>1893</t>
+  </si>
+  <si>
+    <t>Piccadilly Circus, Londres</t>
+  </si>
+  <si>
+    <t>Éros (fontaine commémorative Shaftesbury)</t>
+  </si>
+  <si>
+    <t>1854-1934</t>
+  </si>
+  <si>
+    <t>Bronze doré et aluminium</t>
+  </si>
+  <si>
+    <t>dimensions monumentales</t>
+  </si>
+  <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Anne Whitney</t>
+  </si>
+  <si>
+    <t>1876</t>
+  </si>
+  <si>
+    <t>United States Capitol, Washington</t>
+  </si>
+  <si>
+    <t>Samuel Adams</t>
+  </si>
+  <si>
+    <t>1821-1915</t>
+  </si>
+  <si>
+    <t>américaine</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Antoine-Louis Barye</t>
+  </si>
+  <si>
+    <t>1832</t>
+  </si>
+  <si>
+    <t>Musée du Louvre, Paris</t>
+  </si>
+  <si>
+    <t>Lion au serpent</t>
+  </si>
+  <si>
+    <t>1795-1875</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>135 × 178 cm</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Antonin Mercié</t>
+  </si>
+  <si>
+    <t>1874</t>
+  </si>
+  <si>
+    <t>Musée du Petit Palais, Paris</t>
+  </si>
+  <si>
+    <t>Gloria Victis</t>
+  </si>
+  <si>
+    <t>1845-1916</t>
+  </si>
+  <si>
+    <t>environ 280 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Statue-de-la-liberte-new-york.jpg/960px-Statue-de-la-liberte-new-york.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Auguste Bartholdi</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>La Liberté éclairant le monde.</t>
+  </si>
+  <si>
+    <t>1834-1904</t>
+  </si>
+  <si>
+    <t>Cuivre repoussé (structure Eiffel)</t>
+  </si>
+  <si>
+    <t>46 m de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg/960px-Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Auguste Rodin</t>
   </si>
   <si>
@@ -62,7 +205,31 @@
     <t>Le Penseur</t>
   </si>
   <si>
-    <t>Musée du Louvre, Paris</t>
+    <t>1840-1917</t>
+  </si>
+  <si>
+    <t>189 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Augustus Saint-Gaudens</t>
+  </si>
+  <si>
+    <t>1897</t>
+  </si>
+  <si>
+    <t>Boston Common, Boston</t>
+  </si>
+  <si>
+    <t>Monument à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
+  </si>
+  <si>
+    <t>1848-1907</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Bertel Thorvaldsen</t>
@@ -77,91 +244,307 @@
     <t>Le Christ</t>
   </si>
   <si>
+    <t>1770-1844</t>
+  </si>
+  <si>
+    <t>environ 275 cm de haut</t>
+  </si>
+  <si>
+    <t>danoise</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Camille Claudel</t>
   </si>
   <si>
-    <t>1893</t>
-  </si>
-  <si>
     <t>La Valse</t>
   </si>
   <si>
+    <t>1864-1943</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>David d'Angers</t>
+  </si>
+  <si>
+    <t>1837</t>
+  </si>
+  <si>
+    <t>Panthéon, Paris</t>
+  </si>
+  <si>
+    <t>Fronton du Panthéon de Paris</t>
+  </si>
+  <si>
+    <t>1788-1856</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>dimensions architecturales</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Edgard Degas</t>
+  </si>
+  <si>
+    <t>1878-1881</t>
+  </si>
+  <si>
+    <t>National Gallery of Art, Washington</t>
+  </si>
+  <si>
+    <t>La Petite Danseuse de quatorze ans (1er modèle en cire)</t>
+  </si>
+  <si>
+    <t>1834-1917</t>
+  </si>
+  <si>
+    <t>Cire (original)</t>
+  </si>
+  <si>
+    <t>98 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Edmonia_Lewis_-_The_death_of_Cleopatra.jpg/960px-Edmonia_Lewis_-_The_death_of_Cleopatra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Edmonia Lewis</t>
+  </si>
+  <si>
+    <t>Smithsonian American Art Museum, Washington</t>
+  </si>
+  <si>
+    <t>La Mort de Cléopâtre</t>
+  </si>
+  <si>
+    <t>1844-1907</t>
+  </si>
+  <si>
+    <t>environ 160 cm de long</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Emmanuel Frémiet</t>
+  </si>
+  <si>
+    <t>1887</t>
+  </si>
+  <si>
+    <t>Musée des Beaux-Arts, Nantes</t>
+  </si>
+  <si>
+    <t>Gorille enlevant une femme</t>
+  </si>
+  <si>
+    <t>1824-1910</t>
+  </si>
+  <si>
+    <t>environ 190 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>François Rude</t>
+  </si>
+  <si>
+    <t>1836</t>
+  </si>
+  <si>
+    <t>Arc de Triomphe, Paris</t>
+  </si>
+  <si>
+    <t>Le Départ des volontaires de 1792 (La Marseillaise)</t>
+  </si>
+  <si>
+    <t>1784-1855</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/The_Broncho_Buster_MET_1986.81.2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Frederic Remington</t>
+  </si>
+  <si>
+    <t>1895</t>
+  </si>
+  <si>
+    <t>Amon Carter Museum of American Art, Fort Worth</t>
+  </si>
+  <si>
+    <t>Le Bronco Buster</t>
+  </si>
+  <si>
+    <t>1861-1909</t>
+  </si>
+  <si>
+    <t>environ 60 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Hiram Powers</t>
+  </si>
+  <si>
+    <t>1844</t>
+  </si>
+  <si>
+    <t>L'Esclave grecque</t>
+  </si>
+  <si>
+    <t>1805-1873</t>
+  </si>
+  <si>
+    <t>environ 166 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>James Pradier</t>
+  </si>
+  <si>
+    <t>1852</t>
+  </si>
+  <si>
+    <t>Sapho</t>
+  </si>
+  <si>
+    <t>1790-1852</t>
+  </si>
+  <si>
+    <t>environ 122 cm de haut</t>
+  </si>
+  <si>
+    <t>suisse</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Jean-Baptiste Carpeaux</t>
   </si>
   <si>
     <t>1869</t>
   </si>
   <si>
-    <t>Musée d'Orsay, Paris</t>
-  </si>
-  <si>
     <t>La Danse (façade de l'Opéra de Paris)</t>
   </si>
   <si>
-    <t>Antoine-Louis Barye</t>
-  </si>
-  <si>
-    <t>1832</t>
-  </si>
-  <si>
-    <t>Lion au serpent</t>
-  </si>
-  <si>
-    <t>François Rude</t>
-  </si>
-  <si>
-    <t>1836</t>
-  </si>
-  <si>
-    <t>Arc de Triomphe, Paris</t>
-  </si>
-  <si>
-    <t>Le Départ des volontaires de 1792 (La Marseillaise)</t>
-  </si>
-  <si>
-    <t>Emmanuel Frémiet</t>
-  </si>
-  <si>
-    <t>1887</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts, Nantes</t>
-  </si>
-  <si>
-    <t>Gorille enlevant une femme</t>
-  </si>
-  <si>
-    <t>James Pradier</t>
-  </si>
-  <si>
-    <t>1852</t>
-  </si>
-  <si>
-    <t>Sapho</t>
-  </si>
-  <si>
-    <t>Augustus Saint-Gaudens</t>
-  </si>
-  <si>
-    <t>1897</t>
-  </si>
-  <si>
-    <t>Boston Common, Boston</t>
-  </si>
-  <si>
-    <t>Monument à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
-  </si>
-  <si>
-    <t>David d'Angers</t>
-  </si>
-  <si>
-    <t>1837</t>
-  </si>
-  <si>
-    <t>Panthéon, Paris</t>
-  </si>
-  <si>
-    <t>Fronton du Panthéon de Paris</t>
+    <t>1827-1875</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste Clésinger</t>
+  </si>
+  <si>
+    <t>La Femme piquée par un serpent</t>
+  </si>
+  <si>
+    <t>1814-1883</t>
+  </si>
+  <si>
+    <t>56,5 × 180 × 70 cm</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Jean-Léon Gérôme</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>Tanagra</t>
+  </si>
+  <si>
+    <t>1824-1904</t>
+  </si>
+  <si>
+    <t>Marbre polychrome et ivoire</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Jef Lambeaux</t>
+  </si>
+  <si>
+    <t>1886-1898</t>
+  </si>
+  <si>
+    <t>Pavillon des Passions humaines, Parc du Cinquantenaire, Bruxelles</t>
+  </si>
+  <si>
+    <t>Les Passions humaines</t>
+  </si>
+  <si>
+    <t>1852-1908</t>
+  </si>
+  <si>
+    <t>belge</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>John Gibson</t>
+  </si>
+  <si>
+    <t>1851-1856</t>
+  </si>
+  <si>
+    <t>Walker Art Gallery, Liverpool</t>
+  </si>
+  <si>
+    <t>La Vénus teintée (Tinted Venus)</t>
+  </si>
+  <si>
+    <t>1790-1866</t>
+  </si>
+  <si>
+    <t>Marbre polychrome</t>
+  </si>
+  <si>
+    <t>environ 175 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Josef Václav Myslbek</t>
+  </si>
+  <si>
+    <t>1887-1924</t>
+  </si>
+  <si>
+    <t>Place Venceslas, Prague</t>
+  </si>
+  <si>
+    <t>Monument équestre à saint Venceslas</t>
+  </si>
+  <si>
+    <t>1848-1922</t>
+  </si>
+  <si>
+    <t>tchèque</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Jules Dalou</t>
@@ -176,49 +559,31 @@
     <t>Le Triomphe de la République</t>
   </si>
   <si>
-    <t>Alfred Gilbert</t>
-  </si>
-  <si>
-    <t>Piccadilly Circus, Londres</t>
-  </si>
-  <si>
-    <t>Éros (fontaine commémorative Shaftesbury)</t>
-  </si>
-  <si>
-    <t>Josef Václav Myslbek</t>
-  </si>
-  <si>
-    <t>1887-1924</t>
-  </si>
-  <si>
-    <t>Place Venceslas, Prague</t>
-  </si>
-  <si>
-    <t>Monument équestre à saint Venceslas</t>
-  </si>
-  <si>
-    <t>Hiram Powers</t>
-  </si>
-  <si>
-    <t>1844</t>
-  </si>
-  <si>
-    <t>National Gallery of Art, Washington</t>
-  </si>
-  <si>
-    <t>L'Esclave grecque</t>
-  </si>
-  <si>
-    <t>John Gibson</t>
-  </si>
-  <si>
-    <t>1851-1856</t>
-  </si>
-  <si>
-    <t>Walker Art Gallery, Liverpool</t>
-  </si>
-  <si>
-    <t>La Vénus teintée (Tinted Venus)</t>
+    <t>1838-1902</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Lorenzo Bartolini</t>
+  </si>
+  <si>
+    <t>1837-1845</t>
+  </si>
+  <si>
+    <t>Nymphe au scorpion</t>
+  </si>
+  <si>
+    <t>1777-1850</t>
+  </si>
+  <si>
+    <t>80 × 180 cm</t>
+  </si>
+  <si>
+    <t>italienne</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Socrates_dying_by_Mark_Antokolsky2.jpg/1280px-Socrates_dying_by_Mark_Antokolsky2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Mark Antokolsky</t>
@@ -233,6 +598,18 @@
     <t>Mort de Socrate</t>
   </si>
   <si>
+    <t>1843-1902</t>
+  </si>
+  <si>
+    <t>dimensions non standardisées</t>
+  </si>
+  <si>
+    <t>russe</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Horseman_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
     <t>Pyotr Klodt</t>
   </si>
   <si>
@@ -245,6 +622,12 @@
     <t>Les Chevaux dressés (groupe du pont Anitchkov)</t>
   </si>
   <si>
+    <t>1805-1867</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Nydia_the_blind_flower_girl_1763.JPG/960px-Nydia_the_blind_flower_girl_1763.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Randolph Rogers</t>
   </si>
   <si>
@@ -257,211 +640,25 @@
     <t>Nydia, la fleuriste aveugle de Pompéi</t>
   </si>
   <si>
+    <t>1825-1892</t>
+  </si>
+  <si>
+    <t>environ 140 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/Emancipation_memorial_MRD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
     <t>Thomas Ball</t>
   </si>
   <si>
-    <t>1876</t>
-  </si>
-  <si>
     <t>Lincoln Park, Washington</t>
   </si>
   <si>
     <t>Monument à l'émancipation (Emancipation Memorial)</t>
   </si>
   <si>
-    <t>Edmonia Lewis</t>
-  </si>
-  <si>
-    <t>Smithsonian American Art Museum, Washington</t>
-  </si>
-  <si>
-    <t>La Mort de Cléopâtre</t>
-  </si>
-  <si>
-    <t>Frederic Remington</t>
-  </si>
-  <si>
-    <t>1895</t>
-  </si>
-  <si>
-    <t>Amon Carter Museum of American Art, Fort Worth</t>
-  </si>
-  <si>
-    <t>Le Bronco Buster</t>
-  </si>
-  <si>
-    <t>Lorenzo Bartolini</t>
-  </si>
-  <si>
-    <t>1837-1845</t>
-  </si>
-  <si>
-    <t>Nymphe au scorpion</t>
-  </si>
-  <si>
-    <t>Antonin Mercié</t>
-  </si>
-  <si>
-    <t>1874</t>
-  </si>
-  <si>
-    <t>Musée du Petit Palais, Paris</t>
-  </si>
-  <si>
-    <t>Gloria Victis</t>
-  </si>
-  <si>
-    <t>Jean-Léon Gérôme</t>
-  </si>
-  <si>
-    <t>1890</t>
-  </si>
-  <si>
-    <t>Tanagra</t>
-  </si>
-  <si>
-    <t>Jef Lambeaux</t>
-  </si>
-  <si>
-    <t>1886-1898</t>
-  </si>
-  <si>
-    <t>Pavillon des Passions humaines, Parc du Cinquantenaire, Bruxelles</t>
-  </si>
-  <si>
-    <t>Les Passions humaines</t>
-  </si>
-  <si>
-    <t>Anne Whitney</t>
-  </si>
-  <si>
-    <t>United States Capitol, Washington</t>
-  </si>
-  <si>
-    <t>Samuel Adams</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg/960px-Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Socrates_dying_by_Mark_Antokolsky2.jpg/1280px-Socrates_dying_by_Mark_Antokolsky2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Horseman_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Nydia_the_blind_flower_girl_1763.JPG/960px-Nydia_the_blind_flower_girl_1763.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/Emancipation_memorial_MRD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Edmonia_Lewis_-_The_death_of_Cleopatra.jpg/960px-Edmonia_Lewis_-_The_death_of_Cleopatra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/The_Broncho_Buster_MET_1986.81.2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Statue-de-la-liberte-new-york.jpg/960px-Statue-de-la-liberte-new-york.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>La Liberté éclairant le monde.</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Auguste Bartholdi</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Albert-Ernest Carrier-Belleuse</t>
-  </si>
-  <si>
-    <t>1863</t>
-  </si>
-  <si>
-    <t>La Bacchante</t>
-  </si>
-  <si>
-    <t>Edgard Degas</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste Clésinger</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1878-1881</t>
-  </si>
-  <si>
-    <t>La Petite Danseuse de quatorze ans (1er modèle en cire)</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>La Femme piquée par un serpent</t>
+    <t>1819-1911</t>
   </si>
 </sst>
 </file>
@@ -520,7 +717,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -543,17 +740,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -564,6 +773,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -893,10 +1105,18 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -939,25 +1159,33 @@
       <c r="AW1" s="3"/>
     </row>
     <row r="2" spans="1:49" s="2" customFormat="1">
-      <c r="A2" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
@@ -1000,25 +1228,33 @@
       <c r="AW2" s="3"/>
     </row>
     <row r="3" spans="1:49" s="2" customFormat="1">
-      <c r="A3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -1061,25 +1297,33 @@
       <c r="AW3" s="3"/>
     </row>
     <row r="4" spans="1:49">
-      <c r="A4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -1122,25 +1366,33 @@
       <c r="AW4" s="3"/>
     </row>
     <row r="5" spans="1:49" s="2" customFormat="1">
-      <c r="A5" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="A5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1183,25 +1435,33 @@
       <c r="AW5" s="3"/>
     </row>
     <row r="6" spans="1:49" s="2" customFormat="1">
-      <c r="A6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -1244,25 +1504,33 @@
       <c r="AW6" s="3"/>
     </row>
     <row r="7" spans="1:49" s="2" customFormat="1">
-      <c r="A7" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="7">
         <v>1886</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="D7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -1305,25 +1573,33 @@
       <c r="AW7" s="3"/>
     </row>
     <row r="8" spans="1:49">
-      <c r="A8" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1366,25 +1642,33 @@
       <c r="AW8" s="3"/>
     </row>
     <row r="9" spans="1:49" s="2" customFormat="1">
-      <c r="A9" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1427,25 +1711,33 @@
       <c r="AW9" s="3"/>
     </row>
     <row r="10" spans="1:49" s="2" customFormat="1">
-      <c r="A10" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1488,25 +1780,33 @@
       <c r="AW10" s="3"/>
     </row>
     <row r="11" spans="1:49">
-      <c r="A11" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1549,25 +1849,33 @@
       <c r="AW11" s="3"/>
     </row>
     <row r="12" spans="1:49">
-      <c r="A12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1610,25 +1918,33 @@
       <c r="AW12" s="3"/>
     </row>
     <row r="13" spans="1:49">
-      <c r="A13" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="A13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1671,25 +1987,33 @@
       <c r="AW13" s="3"/>
     </row>
     <row r="14" spans="1:49">
-      <c r="A14" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1732,25 +2056,33 @@
       <c r="AW14" s="3"/>
     </row>
     <row r="15" spans="1:49">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="G15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1793,25 +2125,33 @@
       <c r="AW15" s="3"/>
     </row>
     <row r="16" spans="1:49">
-      <c r="A16" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="A16" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1854,25 +2194,33 @@
       <c r="AW16" s="3"/>
     </row>
     <row r="17" spans="1:49">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="I17" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -1915,25 +2263,33 @@
       <c r="AW17" s="3"/>
     </row>
     <row r="18" spans="1:49">
-      <c r="A18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="A18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -1976,25 +2332,33 @@
       <c r="AW18" s="3"/>
     </row>
     <row r="19" spans="1:49">
-      <c r="A19" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="A19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -2037,25 +2401,33 @@
       <c r="AW19" s="3"/>
     </row>
     <row r="20" spans="1:49">
-      <c r="A20" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="A20" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
@@ -2098,25 +2470,33 @@
       <c r="AW20" s="3"/>
     </row>
     <row r="21" spans="1:49" s="2" customFormat="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="10">
+      <c r="B21" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="9">
         <v>1847</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="D21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
@@ -2159,25 +2539,33 @@
       <c r="AW21" s="3"/>
     </row>
     <row r="22" spans="1:49">
-      <c r="A22" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="A22" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -2220,25 +2608,33 @@
       <c r="AW22" s="3"/>
     </row>
     <row r="23" spans="1:49">
-      <c r="A23" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -2281,25 +2677,33 @@
       <c r="AW23" s="3"/>
     </row>
     <row r="24" spans="1:49">
-      <c r="A24" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="A24" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -2342,25 +2746,33 @@
       <c r="AW24" s="3"/>
     </row>
     <row r="25" spans="1:49">
-      <c r="A25" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="A25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -2403,25 +2815,33 @@
       <c r="AW25" s="3"/>
     </row>
     <row r="26" spans="1:49">
-      <c r="A26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="A26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -2464,25 +2884,33 @@
       <c r="AW26" s="3"/>
     </row>
     <row r="27" spans="1:49">
-      <c r="A27" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="A27" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>186</v>
+      </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -2525,25 +2953,33 @@
       <c r="AW27" s="3"/>
     </row>
     <row r="28" spans="1:49">
-      <c r="A28" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="A28" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -2586,25 +3022,33 @@
       <c r="AW28" s="3"/>
     </row>
     <row r="29" spans="1:49">
-      <c r="A29" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="A29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -2647,25 +3091,33 @@
       <c r="AW29" s="3"/>
     </row>
     <row r="30" spans="1:49">
-      <c r="A30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="A30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -2708,25 +3160,33 @@
       <c r="AW30" s="3"/>
     </row>
     <row r="31" spans="1:49">
-      <c r="A31" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="A31" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -3321,40 +3781,37 @@
       <c r="AW43" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E32">
-    <sortCondition ref="B2:B32"/>
-  </sortState>
   <hyperlinks>
-    <hyperlink ref="A8" r:id="rId1" xr:uid="{93AE980A-6B12-46F0-A8CF-A0D01340DED5}"/>
-    <hyperlink ref="A10" r:id="rId2" xr:uid="{0279C923-D2AA-4264-A899-0BCAFCC5DD8C}"/>
-    <hyperlink ref="A11" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{53D6ACD5-B359-40B4-A22C-BB1BD3A81A04}"/>
-    <hyperlink ref="A20" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C9618ED-B2D7-4284-AD04-539CA4892DAB}"/>
-    <hyperlink ref="A5" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{37B3A290-0452-476D-8FC2-55660C65251D}"/>
-    <hyperlink ref="A16" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B0DB905-2A62-400D-AF1A-5AD350CF3CD4}"/>
-    <hyperlink ref="A15" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7DDC986B-350E-4853-AFD0-B0E19187033D}"/>
-    <hyperlink ref="A19" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AF2F99B6-B0A4-4A9F-A44A-080AD9DF2FFA}"/>
-    <hyperlink ref="A9" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6A325E4D-8BB3-40C0-87DB-8F413F02DF10}"/>
-    <hyperlink ref="A12" r:id="rId10" xr:uid="{4B3D9FD6-66B2-486E-91BD-1D9D62B49EB7}"/>
-    <hyperlink ref="A26" r:id="rId11" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E5AA8D6E-B554-44B0-9598-E37ED9C0B7BD}"/>
-    <hyperlink ref="A3" r:id="rId12" xr:uid="{5A5F0717-4C25-4354-B29B-0BB266B96FCF}"/>
-    <hyperlink ref="A25" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{23816190-EF7C-44C9-ADDC-EAA4146655D3}"/>
-    <hyperlink ref="A18" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7CC8B167-A92F-4D6C-89C1-9BE59C7CF5A4}"/>
-    <hyperlink ref="A24" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{92062880-0FD1-4CE9-A7CF-BDDB3CA8A045}"/>
-    <hyperlink ref="A28" r:id="rId16" xr:uid="{843C53DE-19DB-442D-B85C-710A65F939C3}"/>
-    <hyperlink ref="A29" r:id="rId17" xr:uid="{4C55E7F3-65D4-41C2-88DF-18F00C27A935}"/>
-    <hyperlink ref="A30" r:id="rId18" xr:uid="{261C79ED-8811-43FF-BD7A-B3653CD9C364}"/>
-    <hyperlink ref="A31" r:id="rId19" xr:uid="{6A6F7BA2-54C9-4A0E-B208-8664C78E75F7}"/>
-    <hyperlink ref="A14" r:id="rId20" xr:uid="{62C8B9DF-387B-4E1A-A861-168C2C139E02}"/>
-    <hyperlink ref="A17" r:id="rId21" xr:uid="{4DD3F97F-7316-49A3-9B11-B959E5E59F76}"/>
-    <hyperlink ref="A27" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8AE5868-74B7-4C36-A835-D4B1EDCBB97C}"/>
-    <hyperlink ref="A6" r:id="rId23" xr:uid="{A4A753D4-9A9F-4B52-ACE5-7932A6E3BF1E}"/>
-    <hyperlink ref="A22" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090BCA57-D77A-4463-8E66-36EC42C0B0F0}"/>
-    <hyperlink ref="A23" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE250664-62F3-4370-B90E-2020D4EB3180}"/>
-    <hyperlink ref="A4" r:id="rId26" xr:uid="{DD90777D-C6DF-4044-9591-4C77E277C2F7}"/>
-    <hyperlink ref="A7" r:id="rId27" xr:uid="{976DAD26-1E55-4BD4-AF6C-2386561AB7EE}"/>
-    <hyperlink ref="A2" r:id="rId28" xr:uid="{17830633-D13B-44E2-A398-05B0D9312C22}"/>
-    <hyperlink ref="A13" r:id="rId29" xr:uid="{C75D6FEC-65CF-4FF8-B661-4610575911B6}"/>
-    <hyperlink ref="A21" r:id="rId30" xr:uid="{A47C825E-3623-4ADD-83EC-C19C17B5E457}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A16" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A18" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A19" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A20" r:id="rId19" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A23" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A24" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A25" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A26" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A27" r:id="rId26" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
